--- a/as.xlsx
+++ b/as.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Amin_Projects\GitHub_Projects\Dataset_Project\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE7ACC57-F7E7-41B2-BA57-32F530A8E55D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,8 +24,808 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="265">
+  <si>
+    <t>incorrect_text</t>
+  </si>
+  <si>
+    <t>correct_text</t>
+  </si>
+  <si>
+    <t>error_category</t>
+  </si>
+  <si>
+    <t>error_subcategory</t>
+  </si>
+  <si>
+    <t>incorrect_phrase</t>
+  </si>
+  <si>
+    <t>correct_phrase</t>
+  </si>
+  <si>
+    <t>explanation</t>
+  </si>
+  <si>
+    <t>مرز پایینی آن با سازند سورگاه و مرز بالایی آن با سازند گورپی به سورت پیوسته است.</t>
+  </si>
+  <si>
+    <t>مرز پایینی آن با سازند سورگاه و مرز بالایی آن با سازند گورپی به صورت پیوسته است.</t>
+  </si>
+  <si>
+    <t>اشکالات املایی و واژگانی</t>
+  </si>
+  <si>
+    <t>کاربرد واژهٔ هم‌آوا یا متشابه با معنای نادرست</t>
+  </si>
+  <si>
+    <t>سورت</t>
+  </si>
+  <si>
+    <t>صورت</t>
+  </si>
+  <si>
+    <t>واژهٔ «سورت» هم‌آوای «صورت» است اما معنای متفاوتی دارد و در اینجا به اشتباه به جای «صورت» (به معنای شکل و حالت) به کار رفته است.</t>
+  </si>
+  <si>
+    <t>کارست در سنگ اهکها به دلیل قابلیت انحلال پذیری زیاد به آسانی توسعه پیدا میکند.</t>
+  </si>
+  <si>
+    <t>کارست در سنگ آهکها به دلیل قابلیت انحلال پذیری زیاد به آسانی توسعه پیدا میکند.</t>
+  </si>
+  <si>
+    <t>غلط املایی متداول</t>
+  </si>
+  <si>
+    <t>اهکها</t>
+  </si>
+  <si>
+    <t>آهکها</t>
+  </si>
+  <si>
+    <t>نوشتن «آهک» به صورت «اهک» یک غلط املایی متداول است و حرف «آ» باید با کلاه نوشته شود.</t>
+  </si>
+  <si>
+    <t>پس از آماده سازی نمونه ها ترکیب شیمیایی ویژگیهای مهندسی و انحلال پذیری آنها مورد ارزیابی قرار گرفت.</t>
+  </si>
+  <si>
+    <t>پس از آماده‌سازی نمونه ها ترکیب شیمیایی ویژگیهای مهندسی و انحلال پذیری آنها مورد ارزیابی قرار گرفت.</t>
+  </si>
+  <si>
+    <t>مغایرت با رسم‌الخط معیار</t>
+  </si>
+  <si>
+    <t>آماده سازی</t>
+  </si>
+  <si>
+    <t>آماده‌سازی</t>
+  </si>
+  <si>
+    <t>طبق رسم‌الخط معیار فرهنگستان، در کلمات مرکب و مشتق باید از نیم‌فاصله استفاده شود و «آماده سازی» بدون نیم‌فاصله مغایر با معیار است.</t>
+  </si>
+  <si>
+    <t>در این پژوهش با استفاده از مطالعات سنگ شناسی و تعیین خصوصیات فیزیکی و مکانیکی نمونه‌جات سنگ آهک سازند ایلام در مقطع تیپ انحلال پذیری و گسترش کارست بررسی گردیده است.</t>
+  </si>
+  <si>
+    <t>در این پژوهش با استفاده از مطالعات سنگ شناسی و تعیین خصوصیات فیزیکی و مکانیکی نمونه های سنگ آهک سازند ایلام در مقطع تیپ انحلال پذیری و گسترش کارست بررسی گردیده است.</t>
+  </si>
+  <si>
+    <t>جمع بستن واژهٔ فارسی با نشانهٔ عربی</t>
+  </si>
+  <si>
+    <t>نمونه‌جات</t>
+  </si>
+  <si>
+    <t>نمونه های</t>
+  </si>
+  <si>
+    <t>واژهٔ «نمونه» یک واژهٔ فارسی است و باید با نشانه‌های جمع فارسی («ها» یا «ان») جمع بسته شود، نه با نشانهٔ عربی «ات».</t>
+  </si>
+  <si>
+    <t>کارست در سنگ آهکها به دلیل قابلیت انحلال پذیری زیاداً به آسانی توسعه پیدا میکند.</t>
+  </si>
+  <si>
+    <t>تنوین‌گذاری واژهٔ فارسی</t>
+  </si>
+  <si>
+    <t>زیاداً</t>
+  </si>
+  <si>
+    <t>زیاد</t>
+  </si>
+  <si>
+    <t>واژهٔ «زیاد» ریشهٔ فارسی دارد و تنوین‌گذاری آن (زیاداً) از نظر دستوری نادرست است. تنوین مخصوص واژه‌های عربی است.</t>
+  </si>
+  <si>
+    <t>دوماً بر اساس آزمایش کلسیمتری و XRF موجود افقهای E و F بیشترین مقدار کربنات کلسیم را دارا است و تفاوت انحلال پذیری در افقهای مختلف سازند را نشان میدهد.</t>
+  </si>
+  <si>
+    <t>همچنین بر اساس آزمایش کلسیمتری و XRF موجود افقهای E و F بیشترین مقدار کربنات کلسیم را دارا است و تفاوت انحلال پذیری در افقهای مختلف سازند را نشان میدهد.</t>
+  </si>
+  <si>
+    <t>تنوین‌گذاری نادرست ترتیب‌ها و ترکیب‌ها</t>
+  </si>
+  <si>
+    <t>دوماً</t>
+  </si>
+  <si>
+    <t>همچنین</t>
+  </si>
+  <si>
+    <t>برای بیان ترتیب در زبان فارسی از واژه‌های «دوم»، «سوم» یا قیدهای عربی مانند «ثانیاً» استفاده می‌شود. ترکیب «دوماً» (دوم + تنوین) نادرست و نامأنوس است.</t>
+  </si>
+  <si>
+    <t>کارست در سنگ آهکها به دلیل قابلیت انحلال پذیری زیاد به آسانی توسعۀ پیدا میکند.</t>
+  </si>
+  <si>
+    <t>خطای تای گرد در واژه‌های عربی</t>
+  </si>
+  <si>
+    <t>توسعۀ</t>
+  </si>
+  <si>
+    <t>توسعه</t>
+  </si>
+  <si>
+    <t>واژهٔ «توسعه» به «ه» مختوم می‌شود و نیازی به تای گرد (ۀ) ندارد، زیرا مضاف‌الیه نیست و در حالت عطف یا اضافه قرار نگرفته است.</t>
+  </si>
+  <si>
+    <t>در حفاریهای نفتی حتیٰ با این سازند برخورد دارند.</t>
+  </si>
+  <si>
+    <t>در حفاریهای نفتی هم با این سازند برخورد دارند.</t>
+  </si>
+  <si>
+    <t>خطای الف مقصوره در واژه‌های عربی</t>
+  </si>
+  <si>
+    <t>حتیٰ</t>
+  </si>
+  <si>
+    <t>هم</t>
+  </si>
+  <si>
+    <t>واژهٔ «حتی» با الف مقصوره (ی) نوشته می‌شود و افزودن علامت مد یا الف کشیده (ٰ) بر روی آن در زبان فارسی و عربی معیار نادرست است. در اینجا جایگزینی واژه نیز با غلط املایی همراه شده است.</t>
+  </si>
+  <si>
+    <t>سازند ایلام از جمله سازندهایی است که در ارتفاعات زاگرس تاثیر زیادی دارد و در برش نمونه شامل ۱۹۵ متر سنگ آهک کرم رنگ است.</t>
+  </si>
+  <si>
+    <t>سازند ایلام از جمله سازندهایی است که در ارتفاعات زاگرس گسترش زیادی دارد و در برش نمونه شامل ۱۹۵ متر سنگ آهک کرم رنگ است.</t>
+  </si>
+  <si>
+    <t>خطای همزهٔ میانی</t>
+  </si>
+  <si>
+    <t>تاثیر</t>
+  </si>
+  <si>
+    <t>گسترش</t>
+  </si>
+  <si>
+    <t>در این خطا، واژهٔ صحیح متن («گسترش») با واژهٔ دارای همزهٔ میانی («تأثیر») جایگزین شده و همزهٔ آن نیز به اشتباه حذف گردیده است که ترکیبی از خطای واژگانی و همزهٔ میانی است.</t>
+  </si>
+  <si>
+    <t>منشاء گسترش کارست در این پژوهش با استفاده از مطالعات سنگ شناسی بررسی گردیده است.</t>
+  </si>
+  <si>
+    <t>گسترش کارست در این پژوهش با استفاده از مطالعات سنگ شناسی بررسی گردیده است.</t>
+  </si>
+  <si>
+    <t>خطای همزهٔ پایانی</t>
+  </si>
+  <si>
+    <t>منشاء</t>
+  </si>
+  <si>
+    <t>منشأ</t>
+  </si>
+  <si>
+    <t>واژهٔ «منشأ» در پایان دارای همزه بر روی کرسی الف است. نوشتن آن به صورت «منشاء» با الف مقصوره یا کشیده نادرست است و در اینجا برای ایجاد خطا به متن افزوده شده است.</t>
+  </si>
+  <si>
+    <t>در این پژوهش به منظور بررسی مسأله انحلال پذیری و گسترش کارست از مطالعات سنگ شناسی استفاده شده است.</t>
+  </si>
+  <si>
+    <t>در این پژوهش به منظور بررسی مسئله انحلال پذیری و گسترش کارست از مطالعات سنگ شناسی استفاده شده است.</t>
+  </si>
+  <si>
+    <t>خطای کرسی همزه</t>
+  </si>
+  <si>
+    <t>مسأله</t>
+  </si>
+  <si>
+    <t>مسئله</t>
+  </si>
+  <si>
+    <t>در واژهٔ «مسئله»، همزه باید بر روی کرسی ی نوشته شود. نوشتن آن به صورت «مسأله» (با همزه بر روی کرسی الف) از نظر رسم‌الخط معیار اشتباه است.</t>
+  </si>
+  <si>
+    <t>فراوانی سنگهای آهکی سبب شده تا در پروژه های مخّتلف مهندسی با این نوع سنگها مواجه باشند.</t>
+  </si>
+  <si>
+    <t>فراوانی سنگهای آهکی سبب شده تا در پروژه های مختلف مهندسی با این نوع سنگها مواجه باشند.</t>
+  </si>
+  <si>
+    <t>تشدیدگذاری نادرست یا غیرضروری</t>
+  </si>
+  <si>
+    <t>مخّتلف</t>
+  </si>
+  <si>
+    <t>مختلف</t>
+  </si>
+  <si>
+    <t>واژهٔ «مختلف» فاقد تشدید است و قرار دادن تشدید بر روی حروف آن (مانند «خ» یا «ل») غیرضروری و از نظر آوایی و املایی نادرست است.</t>
+  </si>
+  <si>
+    <t>کَرست در سنگ آهکها به دلیل قابلیت انحلال پذیری زیاد به آسانی توسعه پیدا میکند.</t>
+  </si>
+  <si>
+    <t>حرکت‌گذاری نادرست یا غیرضروری</t>
+  </si>
+  <si>
+    <t>کَرست</t>
+  </si>
+  <si>
+    <t>کارست</t>
+  </si>
+  <si>
+    <t>واژهٔ «کارست» با الف خوانده می‌شود و قرار دادن حرکت فتحه (ـَ) بر روی حرف «ک» و حذف الف، حرکت‌گذاری نادرست و مغایر با تلفظ صحیح واژه است.</t>
+  </si>
+  <si>
+    <t>مرز پایینی آن با سازند سورگاه و مرز بالایی آن با سازند گورپی به‌پیوستگی است.</t>
+  </si>
+  <si>
+    <t>ساخت قید نامأنوس با «به + صفت»</t>
+  </si>
+  <si>
+    <t>به‌پیوستگی</t>
+  </si>
+  <si>
+    <t>به صورت پیوسته</t>
+  </si>
+  <si>
+    <t>ساخت قید با افزودن «به» به اسم مصدر یا صفت (مانند به‌پیوستگی به جای پیوسته یا به‌صورت پیوسته) در فارسی نامأنوس است و باید از صفت یا قید استاندارد استفاده شود.</t>
+  </si>
+  <si>
+    <t>در پایان تعظیمی از این معما را به صورت مسئله ای مطرح میکنیم.</t>
+  </si>
+  <si>
+    <t>در پایان تعمیمی از این معما را به صورت مسئله ای مطرح میکنیم.</t>
+  </si>
+  <si>
+    <t>تعظیمی</t>
+  </si>
+  <si>
+    <t>تعمیمی</t>
+  </si>
+  <si>
+    <t>واژهٔ «تعظیم» به معنای فروتنی و احترام است، در حالی که در اینجا منظور «تعمیم» به معنای کلیت بخشیدن و گسترش دادن یک قاعده است. این دو واژه هم‌آوا هستند اما معنای کاملاً متفاوتی دارند.</t>
+  </si>
+  <si>
+    <t>ابتدا چند نکته را برای رفع برخی از ابهام ها در اطاق فکر می آوریم.</t>
+  </si>
+  <si>
+    <t>ابتدا چند نکته را برای رفع برخی از ابهام ها در اتاق فکر می آوریم.</t>
+  </si>
+  <si>
+    <t>اطاق</t>
+  </si>
+  <si>
+    <t>اتاق</t>
+  </si>
+  <si>
+    <t>نوشتن واژهٔ «اتاق» به صورت «اطاق» یک غلط املایی متداول است. در زبان فارسی صدای «ت» در این واژه با حرف «ت» نوشته می‌شود و استفاده از «ط» نادرست است.</t>
+  </si>
+  <si>
+    <t>چکیده سالها پیش ریموند اسمولیان منطق دان و استاد طرح معما مسئله ای مطرح کرد</t>
+  </si>
+  <si>
+    <t>چکیده سال‌ها پیش ریموند اسمولیان منطق‌دان و استاد طرح معما مسئله‌ای مطرح کرد</t>
+  </si>
+  <si>
+    <t>سالها</t>
+  </si>
+  <si>
+    <t>سال‌ها</t>
+  </si>
+  <si>
+    <t>بر اساس رسم‌الخط معیار فرهنگستان زبان و ادب فارسی، پسوند جمع «ها» و «ان» باید با نیم‌فاصله به واژهٔ پیش از خود متصل شود. نوشتن آن به صورت سرهم («سالها») مغایر با استاندارد املایی است.</t>
+  </si>
+  <si>
+    <t>ابتدا چند نکته را برای رفع برخی از ابهامات می آوریم.</t>
+  </si>
+  <si>
+    <t>ابتدا چند نکته را برای رفع برخی از ابهام ها می آوریم.</t>
+  </si>
+  <si>
+    <t>ابهامات</t>
+  </si>
+  <si>
+    <t>ابهام‌ها</t>
+  </si>
+  <si>
+    <t>واژهٔ «ابهام» اگرچه ریشهٔ عربی دارد، اما در زبان فارسی کاملاً جا افتاده است و بر اساس دستور خط معیار، جمع بستن واژه‌های فارسی‌شده با نشانهٔ عربی «ات» نادرست است و باید از «ها» استفاده شود.</t>
+  </si>
+  <si>
+    <t>ایزدبانوان زبان میدانند اما به همه سؤالها به زبان خودشان پاسخ میدهند</t>
+  </si>
+  <si>
+    <t>ایزدبانوان زبان می‌دانند اما به همهٔ سؤال‌ها به زبان خودشان پاسخ می‌دهند</t>
+  </si>
+  <si>
+    <t>همهٔ</t>
+  </si>
+  <si>
+    <t>همه</t>
+  </si>
+  <si>
+    <t>تنوین‌گذاری (مانند «همهٔ» یا «همه‌اً») برای واژه‌های فارسی مانند «همه» کاملاً نادرست است. تنوین مختص واژه‌های عربی است و در زبان فارسی تنها در برخی قیدهای عربی‌شده (مانند «قطعاً») کاربرد دارد.</t>
+  </si>
+  <si>
+    <t>اینکه ثانیاً سؤال چیست و خطاب به کدام ایزدبانو مطرح میشود</t>
+  </si>
+  <si>
+    <t>اینکه دومین سؤال چیست و خطاب به کدام ایزدبانو مطرح میشود</t>
+  </si>
+  <si>
+    <t>ثانیاً</t>
+  </si>
+  <si>
+    <t>دومین</t>
+  </si>
+  <si>
+    <t>استفاده از قیدهای ترتیبی عربی تنوین‌دار مانند «ثانیاً» به جای «دوم» یا «دومین» در متون فارسی معیار نادرست و نامأنوس است. در زبان فارسی باید از معادل‌های فارسی مانند «دوم» یا «دومین» استفاده کرد.</t>
+  </si>
+  <si>
+    <t>شرح های دیگری بر این معما و راه حل بولس در دایرة المعارف نگاشته شد</t>
+  </si>
+  <si>
+    <t>شرح های دیگری بر این معما و راه حل بولس در دایره المعارف نگاشته شد</t>
+  </si>
+  <si>
+    <t>دایرة</t>
+  </si>
+  <si>
+    <t>دایره</t>
+  </si>
+  <si>
+    <t>در واژه‌های عربی که در زبان فارسی کاربرد دارند، مانند «دایره»، نباید از «تای گرد» (ة) استفاده کرد. شکل صحیح آن در خط فارسی «دایره» است و «ة» مختص عربی است.</t>
+  </si>
+  <si>
+    <t>این قسمت آخر را جان مکارتی، متخصص علوم رایانه به معما افزوده است.</t>
+  </si>
+  <si>
+    <t>این قسمت آخر را جان مک‌کارتی، متخصص علوم رایانه به معما افزوده است.</t>
+  </si>
+  <si>
+    <t>مکارتی</t>
+  </si>
+  <si>
+    <t>مک‌کارتی</t>
+  </si>
+  <si>
+    <t>در نوشتن نام‌های خارجی یا واژه‌های دخیل که در اصل دارای «الف مقصوره» (ی بدون نقطه در عربی) هستند، مانند نام «McCarthy»، باید دقت کرد که شکل صحیح آن در فارسی «مک‌کارتی» است و استفاده از «مکارتی» (با الف معمولی) از نظر آوایی و رسم‌الخطی نادرست است.</t>
+  </si>
+  <si>
+    <t>مسأله این است که هویت A B و C را با طرح سه سؤال روشن کنیم</t>
+  </si>
+  <si>
+    <t>مسئله این است که هویت A B و C را با طرح سه سؤال روشن کنیم</t>
+  </si>
+  <si>
+    <t>بر اساس دستور خط مصوب فرهنگستان، همزهٔ میانی در واژهٔ «مسئله» باید روی خط (دندانه) نوشته شود. نوشتن آن به صورت «مسأله» (همزه روی الف) نادرست است.</t>
+  </si>
+  <si>
+    <t>تصادف برای هر سؤال بله خیری که پرسیده شود منشأ پاسخ خواهد داد.</t>
+  </si>
+  <si>
+    <t>در واژهٔ «منشأ»، همزهٔ پایانی باید روی خط نوشته شود. نوشتن آن به صورت «منشاء» (همزه روی الف) غلط املایی است، زیرا این واژه در فارسی بر روی «ا» تلفظ نمی‌شود و همزهٔ آن روی خط است.</t>
+  </si>
+  <si>
+    <t>جورج بولس در پاسخ به این معما میگوید ابتدا باید ایزدبانویی را شناسایی کرد که تائید شود.</t>
+  </si>
+  <si>
+    <t>جورج بولس در پاسخ به این معما میگوید ابتدا باید ایزدبانویی را شناسایی کرد که تأیید شود.</t>
+  </si>
+  <si>
+    <t>تائید</t>
+  </si>
+  <si>
+    <t>تأیید</t>
+  </si>
+  <si>
+    <t>همزهٔ واژهٔ «تأیید» باید روی حرف «أ» (الف با کلاه) نوشته شود. نوشتن آن به صورت «تائید» (همزه روی ی) از خطاهای رایج املایی است و شکل معیار آن «تأیید» است.</t>
+  </si>
+  <si>
+    <t>او خالق این معما را ریموند اسمولیان می‌داند و به آن معما عنوان دشوارترین معمای منطقی همهٔ دوران‌ها را داد.</t>
+  </si>
+  <si>
+    <t>دشوارترین</t>
+  </si>
+  <si>
+    <t>حرف «ر» در واژهٔ «دشوارترین» نیازی به تشدید ندارد. تشدیدگذاری غیرضروری روی این حرف یک خطای تایپی و املایی محسوب می‌شود و شکل صحیح آن بدون تشدید است.</t>
+  </si>
+  <si>
+    <t>ریموند اسمولیان، فیلسوف، منطق‌دان و ریاضی‌دان آمریکایی خالق معماهای منطقی بسیاری است.</t>
+  </si>
+  <si>
+    <t>آمریکایی</t>
+  </si>
+  <si>
+    <t>حرکت‌گذاری (اعراب‌گذاری) کلمات در متون فارسی معیار، به‌ویژه در متون دانشگاهی و آکادمیک، مگر در موارد خاص مانند آموزش زبان یا رفع ابهام، غیرضروری و نادرست است. قرار دادن حرکت روی حروف واژه‌هایی مانند «آمریکایی» اشتباه است.</t>
+  </si>
+  <si>
+    <t>در این مقاله تلاش میکنیم با استفاده از منطق گزاره ها درک راه حل بولس را به‌آسانی آسان تر کنیم.</t>
+  </si>
+  <si>
+    <t>در این مقاله تلاش میکنیم با استفاده از منطق گزاره ها درک راه حل بولس را آسان تر کنیم.</t>
+  </si>
+  <si>
+    <t>به‌آسانی</t>
+  </si>
+  <si>
+    <t>آسان</t>
+  </si>
+  <si>
+    <t>ساخت قید با استفاده از حرف اضافهٔ «به» + صفت (مانند «به‌آسانی» به جای «آسان» یا «به‌کندی» به جای «کند») در زبان فارسی معیار نامأنوس و نادرست است. در اینجا باید مستقیماً از خود صفت به عنوان قید استفاده شود.</t>
+  </si>
+  <si>
+    <t>چکیده سالها پیش ریموند اسمولیان منطق دان و استاد طرح معما مسئله ای مطرح کرد که جورج بولس عنوان «دشوارترین معمای منطقی همه دورانها را به آن داد در این مقاله ابتدا این معما را بیان و سپس پاسخ جورج بولس را شرح میدهیم در پایان تعمیمی از این معما را به صورت مسئله ای مطمح میکنیم.</t>
+  </si>
+  <si>
+    <t>چکیده سالها پیش ریموند اسمولیان منطق دان و استاد طرح معما مسئله ای مطرح کرد که جورج بولس عنوان «دشوارترین معمای منطقی همه دورانها را به آن داد در این مقاله ابتدا این معما را بیان و سپس پاسخ جورج بولس را شرح میدهیم در پایان تعمیمی از این معما را به صورت مسئله ای مطرح میکنیم.</t>
+  </si>
+  <si>
+    <t>مطمح</t>
+  </si>
+  <si>
+    <t>مطرح</t>
+  </si>
+  <si>
+    <t>واژهٔ «مطمح» به معنی «محل نظر و طمع» است و با «مطرح» به معنی «عنوان‌شده و ارائه‌شده» به دلیل تشابه آوایی و نگارشی جابه‌جا به کار رفته است.</t>
+  </si>
+  <si>
+    <t>منظور از اینکه ایزدبانوی تصادف صادقانه یا کاذبانه سخن میگوید این است که صدق و کذب سخن او به نتیجه پرتاب سکه ای خیالی در ذهنش بستگی دارد اگر نتیجه پرتاب سکه شیر باشد صادقانه سخن میگوید و اگر خط باشد کاذبانه، درست مثل پرتاب یک سکه در یک اطاق خلوت.</t>
+  </si>
+  <si>
+    <t>منظور از اینکه ایزدبانوی تصادف صادقانه یا کاذبانه سخن میگوید این است که صدق و کذب سخن او به نتیجه پرتاب سکه ای خیالی در ذهنش بستگی دارد اگر نتیجه پرتاب سکه شیر باشد صادقانه سخن میگوید و اگر خط باشد کاذبانه، درست مثل پرتاب یک سکه در یک اتاق خلوت.</t>
+  </si>
+  <si>
+    <t>نگارش واژهٔ فارسی «اتاق» با حرف «ط» غلط املایی متداول است و باید با «ت» نوشته شود.</t>
+  </si>
+  <si>
+    <t>ایزدبانوان زبان میدانند اما به همه سؤالها به زبان خودشان پاسخ میدهند که در آن زبان برای «بله» و «خیر» از «دا» و «ها» استفاده میشود حتا اگر ندانید کدام واژه کدام معنی را دارد.</t>
+  </si>
+  <si>
+    <t>ایزدبانوان زبان میدانند اما به همه سؤالها به زبان خودشان پاسخ میدهند که در آن زبان برای «بله» و «خیر» از «دا» و «ها» استفاده میشود حتی اگر ندانید کدام واژه کدام معنی را دارد.</t>
+  </si>
+  <si>
+    <t>حتا</t>
+  </si>
+  <si>
+    <t>حتی</t>
+  </si>
+  <si>
+    <t>مطابق با رسم‌الخط معیار مصوب فرهنگستان زبان و ادب فارسی، حرف ربط «حتی» باید با «ی» پایانی نوشته شود و نگارش آن با الف («حتا») مغایر با رسم‌الخط معیار است.</t>
+  </si>
+  <si>
+    <t>در مقاله [۴] نیز با طرح پرسشی و سپس ساده کردن شرایط معما و البته فاصله گرفتن معما از معمای اصلی آن را حل کرده اند؛ گزارشات دیگری نیز در این زمینه ارائه شده است.</t>
+  </si>
+  <si>
+    <t>در مقاله [۴] نیز با طرح پرسشی و سپس ساده کردن شرایط معما و البته فاصله گرفتن معما از معمای اصلی آن را حل کرده اند؛ گزارش‌های دیگری نیز در این زمینه ارائه شده است.</t>
+  </si>
+  <si>
+    <t>گزارشات</t>
+  </si>
+  <si>
+    <t>گزارش‌ها</t>
+  </si>
+  <si>
+    <t>واژهٔ «گزارش» ریشهٔ فارسی دارد و نباید با نشانهٔ جمع عربی «ات» جمع بسته شود؛ شکل درست آن «گزارش‌ها» است.</t>
+  </si>
+  <si>
+    <t>اینکه دومین سؤال چیست و خطاب به کدام ایزدبانو مطرح میشود، گاهاً ممکن است به پاسخ سؤال اول بستگی داشته باشد و چنین است در مورد سؤال سوم)؛</t>
+  </si>
+  <si>
+    <t>اینکه دومین سؤال چیست و خطاب به کدام ایزدبانو مطرح میشود، ممکن است به پاسخ سؤال اول بستگی داشته باشد و چنین است در مورد سؤال سوم)؛</t>
+  </si>
+  <si>
+    <t>گاهاً</t>
+  </si>
+  <si>
+    <t>گاه / گاهی</t>
+  </si>
+  <si>
+    <t>واژهٔ «گاه» فارسی است و افزودن نشانهٔ تنوین عربی به کلمات اصیل فارسی از نظر قواعد زبان نادرست است.</t>
+  </si>
+  <si>
+    <t>اینکه دوماً سؤال چیست و خطاب به کدام ایزدبانو مطرح میشود، ممکن است به پاسخ سؤال اول بستگی داشته باشد و چنین است در مورد سؤال سوم)؛</t>
+  </si>
+  <si>
+    <t>دوم / در درجهٔ دوم / ثانیاً</t>
+  </si>
+  <si>
+    <t>کلمهٔ «دوم» فارسی است و پذیرش تنوین برای ترتیب‌ها به‌صورت «دوماً» یا «سوماً» نادرست است؛ باید از «دوم»، «ثانیاً» یا «در مرحلهٔ دوم» استفاده شود.</t>
+  </si>
+  <si>
+    <t>این معما از این قرار است سه ایزدبانوی B A و C با دایرة المعارف منطقی گسترده، صدق كذب و تصادف نامیده شده اند.</t>
+  </si>
+  <si>
+    <t>این معما از این قرار است سه ایزدبانوی B A و C با دایره المعارف منطقی گسترده، صدق كذب و تصادف نامیده شده اند.</t>
+  </si>
+  <si>
+    <t>دایرة المعارف</t>
+  </si>
+  <si>
+    <t>دایره المعارف / دایرةالمعارف</t>
+  </si>
+  <si>
+    <t>استفاده از تای گرد (ة) به جای «ه» در واژه‌های رایج زبان فارسی، مگر در برخی ترکیبات خاص، نادرست است و باید «دایره‌المعارف» یا با رعایت هکسره نوشته شود.</t>
+  </si>
+  <si>
+    <t>ریموند اسمولیان، فیلسوف، منطق دان و ریاضی دان آمریکایی خالق معماهای منطقی بسیاری است که میتوان آنها را با استدلالی حتیٰ عمیق تر بازخوانی کرد.</t>
+  </si>
+  <si>
+    <t>ریموند اسمولیان، فیلسوف، منطق دان و ریاضی دان آمریکایی خالق معماهای منطقی بسیاری است که میتوان آنها را با استدلالی حتی عمیق تر بازخوانی کرد.</t>
+  </si>
+  <si>
+    <t>گذاشتن علامت الف مقصوره (ٰ) بر روی واژه‌های تثبیت‌شده در زبان فارسی مانند «حتی»، «عیسی» و «موسی» غیرضروری و خلاف رسم‌الخط معیار است.</t>
+  </si>
+  <si>
+    <t>مسئله این است که هویت B A و C را با طرح سه سوئال بله خیر سؤالی که پاسخ آن تنها «بله» یا «خیر» است روشن کنیم</t>
+  </si>
+  <si>
+    <t>مسئله این است که هویت B A و C را با طرح سه سؤال بله خیر سؤالی که پاسخ آن تنها «بله» یا «خیر» است روشن کنیم</t>
+  </si>
+  <si>
+    <t>سوئال</t>
+  </si>
+  <si>
+    <t>سؤال</t>
+  </si>
+  <si>
+    <t>نگارش همزهٔ میانی در واژهٔ «سؤال» به‌صورت واو و همزه مستقل («سوئال» یا «سئوال») غلط است و کرسی صحیح آن واو همزه‌دار («ؤ») است.</t>
+  </si>
+  <si>
+    <t>بولس در پاسخ به این معما میگوید ابتدا باید ایزدبانویی را شناسایی کرد که مبداء و منشاء تصادف است و نه صدق یا کذب»؛</t>
+  </si>
+  <si>
+    <t>بولس در پاسخ به این معما میگوید ابتدا باید ایزدبانویی را شناسایی کرد که مبدأ و منشأ تصادف است و نه صدق یا کذب»؛</t>
+  </si>
+  <si>
+    <t>واژه‌های مختوم به همزهٔ ماقبل‌مفتوح عربی نظیر «منشأ» و «مبدأ» با الف و همزه روی آن نوشته می‌شوند و نگارش آن‌ها به‌صورت الف و همزهٔ منفصل («منشاء») خطاست.</t>
+  </si>
+  <si>
+    <t>شرح های دیگری بر این معما و راه حل بولس تائید و نگاشته شد؛ در [۶] [۹]، [۵] و [۱۰] میتوان برخی از دیگر شرح ها را دید.</t>
+  </si>
+  <si>
+    <t>شرح های دیگری بر این معما و راه حل بولس تأیید و نگاشته شد؛ در [۶] [۹]، [۵] و [۱۰] میتوان برخی از دیگر شرح ها را دید.</t>
+  </si>
+  <si>
+    <t>در واژهٔ «تأیید»، همزه ماقبل‌مفتوح بوده و کرسی مناسب آن الف («أ») است؛ نگارش آن روی دندانه به‌صورت «تائید» غلط کرسی همزه محسوب می‌شود.</t>
+  </si>
+  <si>
+    <t>این قسمت آخر را جان مکارتی، متخصّص علوم رایانه به معما افزوده است.</t>
+  </si>
+  <si>
+    <t>متخصّص</t>
+  </si>
+  <si>
+    <t>متخصص</t>
+  </si>
+  <si>
+    <t>گذاشتن تشدید روی واژه‌های متداول فارسی/عربی در متون علمی که ایجاد ابهام معنایی نمی‌کنند، غیرضروری و مغایر با اصل پیراستگی خط معیار است.</t>
+  </si>
+  <si>
+    <t>در این مقاله ابتدا این مُعَمّا را بیان و سپس پاسخ جورج بولس را شرح میدهیم</t>
+  </si>
+  <si>
+    <t>در این مقاله ابتدا این معما را بیان و سپس پاسخ جورج بولس را شرح میدهیم</t>
+  </si>
+  <si>
+    <t>مُعَمّا</t>
+  </si>
+  <si>
+    <t>معما</t>
+  </si>
+  <si>
+    <t>حرکت‌گذاری و اعراب‌گذاری کامل کلمات روان و شناخته‌شده در متون دانشگاهی غیرضروری بوده و بار بصری متن را مخدوش می‌کند.</t>
+  </si>
+  <si>
+    <t>در این مقاله تلاش میکنیم با استفاده از منطق گزاره ها جدول منطقی و استدلال قیاسی به‌آسانی درک راه حل بولس را میسر کنیم.</t>
+  </si>
+  <si>
+    <t>در این مقاله تلاش میکنیم با استفاده از منطق گزاره ها جدول منطقی و استدلال قیاسی آسان تر درک راه حل بولس را میسر کنیم.</t>
+  </si>
+  <si>
+    <t>آسان‌تر / به آسانی</t>
+  </si>
+  <si>
+    <t>ساختن قید با ترکیب «به + صفت/اسم» به‌صورت چسبیده و نامأنوس (نظیر به‌کندی، به‌سختی، به‌آسانی) در ساختار نحوی فصیح دانشگاهی گرته‌برداری نامناسب تلقی می‌شود و کاربرد صفت در نقش قیدی اولویت دارد.</t>
+  </si>
+  <si>
+    <t>این گره یا ریشه همان مسئله یا ایده‌ای است که در خال تحلیل و بررسی آن هستیم.</t>
+  </si>
+  <si>
+    <t>این گره یا ریشه همان مسئله یا ایده‌ای است که در حال تحلیل و بررسی آن هستیم.</t>
+  </si>
+  <si>
+    <t>در خال تحلیل</t>
+  </si>
+  <si>
+    <t>در حال تحلیل</t>
+  </si>
+  <si>
+    <t>واژه «خال» به معنی لکه یا خال صورت است و با «حال» در نوشتار متشابه است؛ در این بافت تنها «حال» معنی «وضعیت» را می‌دهد.</t>
+  </si>
+  <si>
+    <t>هریک از پرسش‌های ۱، ۲ و ۳ را می‌توان با یک جدول ارزش منطقی مورد برسی قرار داد.</t>
+  </si>
+  <si>
+    <t>هریک از پرسش‌های ۱، ۲ و ۳ را می‌توان با یک جدول ارزش منطقی مورد بررسی قرار داد.</t>
+  </si>
+  <si>
+    <t>برسی</t>
+  </si>
+  <si>
+    <t>بررسی</t>
+  </si>
+  <si>
+    <t>املای صحیح «بررسی» با دو «ر» است؛ حذف یکی از آن‌ها غلط املایی متداول به‌شمار می‌آید.</t>
+  </si>
+  <si>
+    <t>ابتدا جدول ۱ مربوط به پرسش ۱ را می آوریم:</t>
+  </si>
+  <si>
+    <t>ابتدا جدول ۱ مربوط به پرسش ۱ را می‌آوریم:</t>
+  </si>
+  <si>
+    <t>می آوریم</t>
+  </si>
+  <si>
+    <t>می‌آوریم</t>
+  </si>
+  <si>
+    <t>در رسم‌الخط معیار فارسی، پیشوند «می» با نیم‌فاصله به فعل می‌چسبد؛ نوشتن آن با فاصله کامل مغایر با استاندارد است.</t>
+  </si>
+  <si>
+    <t>برای ساده‌تر شدن کار، برای گزاره‌جات زیر نامی انتخاب می‌کنیم:</t>
+  </si>
+  <si>
+    <t>برای ساده‌تر شدن کار، برای گزاره‌های زیر نامی انتخاب می‌کنیم:</t>
+  </si>
+  <si>
+    <t>گزاره‌جات</t>
+  </si>
+  <si>
+    <t>گزاره‌ها</t>
+  </si>
+  <si>
+    <t>واژه فارسی «گزاره» نباید با نشانه جمع عربی «-ات» جمع بسته شود؛ صورت صحیح فارسی «گزاره‌ها» است.</t>
+  </si>
+  <si>
+    <t>برای راحتیاً کار خواننده توضیحاتی در مورد نمودار درختی می‌آوریم؛ اطلاعات بیشتر در [۲] آمده است.</t>
+  </si>
+  <si>
+    <t>برای راحتی کار خواننده توضیحاتی در مورد نمودار درختی می‌آوریم؛ اطلاعات بیشتر در [۲] آمده است.</t>
+  </si>
+  <si>
+    <t>راحتیاً</t>
+  </si>
+  <si>
+    <t>راحتی</t>
+  </si>
+  <si>
+    <t>تنوین فقط به واژه‌های عربی افزوده می‌شود؛ واژه فارسی «راحتی» نباید تنوین بگیرد.</t>
+  </si>
+  <si>
+    <t>برای راحتی کار خواننده توضیحاتی در مورد نمودار درختی می‌آوریم؛ دوماً اطلاعات بیشتر در [۲] آمده است.</t>
+  </si>
+  <si>
+    <t>دوم</t>
+  </si>
+  <si>
+    <t>برای اشاره ترتیبی در فارسی نباید از تنوین «اً» استفاده کرد؛ «دوماً» ترکیبی نادرست است و به‌جای آن «دوم» یا عبارت بدون تنوین به کار می‌رود.</t>
+  </si>
+  <si>
+    <t>این گره یا ریشه همان مسئلت یا ایده‌ای است که در حال تحلیل و بررسی آن هستیم.</t>
+  </si>
+  <si>
+    <t>مسئلت</t>
+  </si>
+  <si>
+    <t>تای گرد (ة) در واژه عربی «مسئله» در فارسی به صورت «ه» نوشته می‌شود؛ تبدیل آن به «ت» خطاست.</t>
+  </si>
+  <si>
+    <t>لذا هریک از پرسش‌های ۱، ۲ و ۳ را می‌توان با یک جدول ارزش منطقا مورد بررسی قرار داد.</t>
+  </si>
+  <si>
+    <t>لذا هریک از پرسش‌های ۱، ۲ و ۳ را می‌توان با یک جدول ارزش منطقی مورد بررسی قرار داد.</t>
+  </si>
+  <si>
+    <t>منطقا</t>
+  </si>
+  <si>
+    <t>منطقی</t>
+  </si>
+  <si>
+    <t>واژه عربی «منطقی» با الف مقصوره در فارسی به صورت «ی» نوشته می‌شود؛ نوشتن آن با «ا» خطاست.</t>
+  </si>
+  <si>
+    <t>این گره یا ریشه همان مسأله یا ایده‌ای است که در حال تحلیل و بررسی آن هستیم.</t>
+  </si>
+  <si>
+    <t>در واژه «مسئله» همزه میانی باید روی «ی» بنشیند؛ نوشتن آن روی «الف» (مسأله) خطاست.</t>
+  </si>
+  <si>
+    <t>ابتداء جدول ۱ مربوط به پرسش ۱ را می‌آوریم:</t>
+  </si>
+  <si>
+    <t>ابتداء</t>
+  </si>
+  <si>
+    <t>ابتدا</t>
+  </si>
+  <si>
+    <t>واژه «ابتدا» در فارسی بدون همزه پایانی نوشته می‌شود؛ افزودن همزه پایانی خطاست.</t>
+  </si>
+  <si>
+    <t>این گره یا ریشه همان مسئله یا ائده‌ای است که در حال تحلیل و بررسی آن هستیم.</t>
+  </si>
+  <si>
+    <t>ائده‌ای</t>
+  </si>
+  <si>
+    <t>ایده‌ای</t>
+  </si>
+  <si>
+    <t>همزه در واژه «ایده» نباید به شکل «ائده» نوشته شود؛ کرسی همزه در این واژه نادرست است.</t>
+  </si>
+  <si>
+    <t>برای ساده‌تر شدن کار، برای گزارّه‌های زیر نامی انتخاب می‌کنیم:</t>
+  </si>
+  <si>
+    <t>گزارّه‌های</t>
+  </si>
+  <si>
+    <t>گزاره‌های</t>
+  </si>
+  <si>
+    <t>افزودن تشدید روی «ر» در واژه «گزاره» غیرضروری و نادرست است.</t>
+  </si>
+  <si>
+    <t>لذا هریک از پرسش‌های ۱، ۲ و ۳ را می‌توان با یک جدول ارزش مَنطِقی مورد بررسی قرار داد.</t>
+  </si>
+  <si>
+    <t>مَنطِقی</t>
+  </si>
+  <si>
+    <t>حرکت‌گذاری حروف در متن فارسی معیار غیرضروری است و واژه «منطقی» بدون حرکت نوشته می‌شود.</t>
+  </si>
+  <si>
+    <t>هریک از گزاره‌های p, q, r, s و t می‌توانند درست یا نادرست (به‌کوتاهی T یا F) باشند.</t>
+  </si>
+  <si>
+    <t>هریک از گزاره‌های p, q, r, s و t می‌توانند درست یا نادرست (به‌اختصار T یا F) باشند.</t>
+  </si>
+  <si>
+    <t>به‌کوتاهی</t>
+  </si>
+  <si>
+    <t>به‌اختصار</t>
+  </si>
+  <si>
+    <t>ساخت قید با «به + صفت کوتاه» در این بافت نامأنوس است؛ شکل معیار «به‌اختصار» است.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -330,10 +1136,1325 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="53.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F10" t="s">
+        <v>58</v>
+      </c>
+      <c r="G10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F11" t="s">
+        <v>64</v>
+      </c>
+      <c r="G11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E12" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12" t="s">
+        <v>70</v>
+      </c>
+      <c r="G12" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>72</v>
+      </c>
+      <c r="B13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E13" t="s">
+        <v>75</v>
+      </c>
+      <c r="F13" t="s">
+        <v>76</v>
+      </c>
+      <c r="G13" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" t="s">
+        <v>79</v>
+      </c>
+      <c r="E14" t="s">
+        <v>80</v>
+      </c>
+      <c r="F14" t="s">
+        <v>81</v>
+      </c>
+      <c r="G14" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>83</v>
+      </c>
+      <c r="B15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" t="s">
+        <v>84</v>
+      </c>
+      <c r="E15" t="s">
+        <v>85</v>
+      </c>
+      <c r="F15" t="s">
+        <v>86</v>
+      </c>
+      <c r="G15" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>88</v>
+      </c>
+      <c r="B16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" t="s">
+        <v>90</v>
+      </c>
+      <c r="F16" t="s">
+        <v>91</v>
+      </c>
+      <c r="G16" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>93</v>
+      </c>
+      <c r="B17" t="s">
+        <v>94</v>
+      </c>
+      <c r="C17" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" t="s">
+        <v>95</v>
+      </c>
+      <c r="F17" t="s">
+        <v>96</v>
+      </c>
+      <c r="G17" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>98</v>
+      </c>
+      <c r="B18" t="s">
+        <v>99</v>
+      </c>
+      <c r="C18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" t="s">
+        <v>100</v>
+      </c>
+      <c r="F18" t="s">
+        <v>101</v>
+      </c>
+      <c r="G18" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>103</v>
+      </c>
+      <c r="B19" t="s">
+        <v>104</v>
+      </c>
+      <c r="C19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E19" t="s">
+        <v>105</v>
+      </c>
+      <c r="F19" t="s">
+        <v>106</v>
+      </c>
+      <c r="G19" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>108</v>
+      </c>
+      <c r="B20" t="s">
+        <v>109</v>
+      </c>
+      <c r="C20" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20" t="s">
+        <v>110</v>
+      </c>
+      <c r="F20" t="s">
+        <v>111</v>
+      </c>
+      <c r="G20" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>113</v>
+      </c>
+      <c r="B21" t="s">
+        <v>114</v>
+      </c>
+      <c r="C21" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" t="s">
+        <v>39</v>
+      </c>
+      <c r="E21" t="s">
+        <v>115</v>
+      </c>
+      <c r="F21" t="s">
+        <v>116</v>
+      </c>
+      <c r="G21" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>118</v>
+      </c>
+      <c r="B22" t="s">
+        <v>119</v>
+      </c>
+      <c r="C22" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" t="s">
+        <v>44</v>
+      </c>
+      <c r="E22" t="s">
+        <v>120</v>
+      </c>
+      <c r="F22" t="s">
+        <v>121</v>
+      </c>
+      <c r="G22" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>123</v>
+      </c>
+      <c r="B23" t="s">
+        <v>124</v>
+      </c>
+      <c r="C23" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" t="s">
+        <v>50</v>
+      </c>
+      <c r="E23" t="s">
+        <v>125</v>
+      </c>
+      <c r="F23" t="s">
+        <v>126</v>
+      </c>
+      <c r="G23" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>128</v>
+      </c>
+      <c r="B24" t="s">
+        <v>129</v>
+      </c>
+      <c r="C24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" t="s">
+        <v>56</v>
+      </c>
+      <c r="E24" t="s">
+        <v>69</v>
+      </c>
+      <c r="F24" t="s">
+        <v>70</v>
+      </c>
+      <c r="G24" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>131</v>
+      </c>
+      <c r="B25" t="s">
+        <v>131</v>
+      </c>
+      <c r="C25" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" t="s">
+        <v>62</v>
+      </c>
+      <c r="E25" t="s">
+        <v>64</v>
+      </c>
+      <c r="F25" t="s">
+        <v>64</v>
+      </c>
+      <c r="G25" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>133</v>
+      </c>
+      <c r="B26" t="s">
+        <v>134</v>
+      </c>
+      <c r="C26" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" t="s">
+        <v>68</v>
+      </c>
+      <c r="E26" t="s">
+        <v>135</v>
+      </c>
+      <c r="F26" t="s">
+        <v>136</v>
+      </c>
+      <c r="G26" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>138</v>
+      </c>
+      <c r="B27" t="s">
+        <v>138</v>
+      </c>
+      <c r="C27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" t="s">
+        <v>74</v>
+      </c>
+      <c r="E27" t="s">
+        <v>139</v>
+      </c>
+      <c r="F27" t="s">
+        <v>139</v>
+      </c>
+      <c r="G27" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>141</v>
+      </c>
+      <c r="B28" t="s">
+        <v>141</v>
+      </c>
+      <c r="C28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" t="s">
+        <v>79</v>
+      </c>
+      <c r="E28" t="s">
+        <v>142</v>
+      </c>
+      <c r="F28" t="s">
+        <v>142</v>
+      </c>
+      <c r="G28" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>144</v>
+      </c>
+      <c r="B29" t="s">
+        <v>145</v>
+      </c>
+      <c r="C29" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" t="s">
+        <v>84</v>
+      </c>
+      <c r="E29" t="s">
+        <v>146</v>
+      </c>
+      <c r="F29" t="s">
+        <v>147</v>
+      </c>
+      <c r="G29" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>149</v>
+      </c>
+      <c r="B30" t="s">
+        <v>150</v>
+      </c>
+      <c r="C30" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" t="s">
+        <v>10</v>
+      </c>
+      <c r="E30" t="s">
+        <v>151</v>
+      </c>
+      <c r="F30" t="s">
+        <v>152</v>
+      </c>
+      <c r="G30" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>154</v>
+      </c>
+      <c r="B31" t="s">
+        <v>155</v>
+      </c>
+      <c r="C31" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" t="s">
+        <v>16</v>
+      </c>
+      <c r="E31" t="s">
+        <v>95</v>
+      </c>
+      <c r="F31" t="s">
+        <v>96</v>
+      </c>
+      <c r="G31" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>157</v>
+      </c>
+      <c r="B32" t="s">
+        <v>158</v>
+      </c>
+      <c r="C32" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" t="s">
+        <v>22</v>
+      </c>
+      <c r="E32" t="s">
+        <v>159</v>
+      </c>
+      <c r="F32" t="s">
+        <v>160</v>
+      </c>
+      <c r="G32" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>162</v>
+      </c>
+      <c r="B33" t="s">
+        <v>163</v>
+      </c>
+      <c r="C33" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" t="s">
+        <v>28</v>
+      </c>
+      <c r="E33" t="s">
+        <v>164</v>
+      </c>
+      <c r="F33" t="s">
+        <v>165</v>
+      </c>
+      <c r="G33" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>167</v>
+      </c>
+      <c r="B34" t="s">
+        <v>168</v>
+      </c>
+      <c r="C34" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" t="s">
+        <v>33</v>
+      </c>
+      <c r="E34" t="s">
+        <v>169</v>
+      </c>
+      <c r="F34" t="s">
+        <v>170</v>
+      </c>
+      <c r="G34" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>172</v>
+      </c>
+      <c r="B35" t="s">
+        <v>168</v>
+      </c>
+      <c r="C35" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" t="s">
+        <v>39</v>
+      </c>
+      <c r="E35" t="s">
+        <v>40</v>
+      </c>
+      <c r="F35" t="s">
+        <v>173</v>
+      </c>
+      <c r="G35" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>175</v>
+      </c>
+      <c r="B36" t="s">
+        <v>176</v>
+      </c>
+      <c r="C36" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" t="s">
+        <v>44</v>
+      </c>
+      <c r="E36" t="s">
+        <v>177</v>
+      </c>
+      <c r="F36" t="s">
+        <v>178</v>
+      </c>
+      <c r="G36" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>180</v>
+      </c>
+      <c r="B37" t="s">
+        <v>181</v>
+      </c>
+      <c r="C37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" t="s">
+        <v>50</v>
+      </c>
+      <c r="E37" t="s">
+        <v>51</v>
+      </c>
+      <c r="F37" t="s">
+        <v>160</v>
+      </c>
+      <c r="G37" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>183</v>
+      </c>
+      <c r="B38" t="s">
+        <v>184</v>
+      </c>
+      <c r="C38" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" t="s">
+        <v>56</v>
+      </c>
+      <c r="E38" t="s">
+        <v>185</v>
+      </c>
+      <c r="F38" t="s">
+        <v>186</v>
+      </c>
+      <c r="G38" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>188</v>
+      </c>
+      <c r="B39" t="s">
+        <v>189</v>
+      </c>
+      <c r="C39" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" t="s">
+        <v>62</v>
+      </c>
+      <c r="E39" t="s">
+        <v>63</v>
+      </c>
+      <c r="F39" t="s">
+        <v>64</v>
+      </c>
+      <c r="G39" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>191</v>
+      </c>
+      <c r="B40" t="s">
+        <v>192</v>
+      </c>
+      <c r="C40" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" t="s">
+        <v>68</v>
+      </c>
+      <c r="E40" t="s">
+        <v>135</v>
+      </c>
+      <c r="F40" t="s">
+        <v>136</v>
+      </c>
+      <c r="G40" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>194</v>
+      </c>
+      <c r="B41" t="s">
+        <v>123</v>
+      </c>
+      <c r="C41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" t="s">
+        <v>74</v>
+      </c>
+      <c r="E41" t="s">
+        <v>195</v>
+      </c>
+      <c r="F41" t="s">
+        <v>196</v>
+      </c>
+      <c r="G41" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>198</v>
+      </c>
+      <c r="B42" t="s">
+        <v>199</v>
+      </c>
+      <c r="C42" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" t="s">
+        <v>79</v>
+      </c>
+      <c r="E42" t="s">
+        <v>200</v>
+      </c>
+      <c r="F42" t="s">
+        <v>201</v>
+      </c>
+      <c r="G42" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>203</v>
+      </c>
+      <c r="B43" t="s">
+        <v>204</v>
+      </c>
+      <c r="C43" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" t="s">
+        <v>84</v>
+      </c>
+      <c r="E43" t="s">
+        <v>146</v>
+      </c>
+      <c r="F43" t="s">
+        <v>205</v>
+      </c>
+      <c r="G43" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>207</v>
+      </c>
+      <c r="B44" t="s">
+        <v>208</v>
+      </c>
+      <c r="C44" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" t="s">
+        <v>10</v>
+      </c>
+      <c r="E44" t="s">
+        <v>209</v>
+      </c>
+      <c r="F44" t="s">
+        <v>210</v>
+      </c>
+      <c r="G44" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>212</v>
+      </c>
+      <c r="B45" t="s">
+        <v>213</v>
+      </c>
+      <c r="C45" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" t="s">
+        <v>16</v>
+      </c>
+      <c r="E45" t="s">
+        <v>214</v>
+      </c>
+      <c r="F45" t="s">
+        <v>215</v>
+      </c>
+      <c r="G45" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>217</v>
+      </c>
+      <c r="B46" t="s">
+        <v>218</v>
+      </c>
+      <c r="C46" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" t="s">
+        <v>22</v>
+      </c>
+      <c r="E46" t="s">
+        <v>219</v>
+      </c>
+      <c r="F46" t="s">
+        <v>220</v>
+      </c>
+      <c r="G46" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>222</v>
+      </c>
+      <c r="B47" t="s">
+        <v>223</v>
+      </c>
+      <c r="C47" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" t="s">
+        <v>28</v>
+      </c>
+      <c r="E47" t="s">
+        <v>224</v>
+      </c>
+      <c r="F47" t="s">
+        <v>225</v>
+      </c>
+      <c r="G47" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>227</v>
+      </c>
+      <c r="B48" t="s">
+        <v>228</v>
+      </c>
+      <c r="C48" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" t="s">
+        <v>33</v>
+      </c>
+      <c r="E48" t="s">
+        <v>229</v>
+      </c>
+      <c r="F48" t="s">
+        <v>230</v>
+      </c>
+      <c r="G48" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>232</v>
+      </c>
+      <c r="B49" t="s">
+        <v>228</v>
+      </c>
+      <c r="C49" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" t="s">
+        <v>39</v>
+      </c>
+      <c r="E49" t="s">
+        <v>40</v>
+      </c>
+      <c r="F49" t="s">
+        <v>233</v>
+      </c>
+      <c r="G49" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>235</v>
+      </c>
+      <c r="B50" t="s">
+        <v>208</v>
+      </c>
+      <c r="C50" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" t="s">
+        <v>44</v>
+      </c>
+      <c r="E50" t="s">
+        <v>236</v>
+      </c>
+      <c r="F50" t="s">
+        <v>70</v>
+      </c>
+      <c r="G50" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>238</v>
+      </c>
+      <c r="B51" t="s">
+        <v>239</v>
+      </c>
+      <c r="C51" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" t="s">
+        <v>50</v>
+      </c>
+      <c r="E51" t="s">
+        <v>240</v>
+      </c>
+      <c r="F51" t="s">
+        <v>241</v>
+      </c>
+      <c r="G51" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>243</v>
+      </c>
+      <c r="B52" t="s">
+        <v>208</v>
+      </c>
+      <c r="C52" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" t="s">
+        <v>56</v>
+      </c>
+      <c r="E52" t="s">
+        <v>69</v>
+      </c>
+      <c r="F52" t="s">
+        <v>70</v>
+      </c>
+      <c r="G52" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>245</v>
+      </c>
+      <c r="B53" t="s">
+        <v>218</v>
+      </c>
+      <c r="C53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D53" t="s">
+        <v>62</v>
+      </c>
+      <c r="E53" t="s">
+        <v>246</v>
+      </c>
+      <c r="F53" t="s">
+        <v>247</v>
+      </c>
+      <c r="G53" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>249</v>
+      </c>
+      <c r="B54" t="s">
+        <v>208</v>
+      </c>
+      <c r="C54" t="s">
+        <v>9</v>
+      </c>
+      <c r="D54" t="s">
+        <v>68</v>
+      </c>
+      <c r="E54" t="s">
+        <v>250</v>
+      </c>
+      <c r="F54" t="s">
+        <v>251</v>
+      </c>
+      <c r="G54" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>253</v>
+      </c>
+      <c r="B55" t="s">
+        <v>223</v>
+      </c>
+      <c r="C55" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55" t="s">
+        <v>74</v>
+      </c>
+      <c r="E55" t="s">
+        <v>254</v>
+      </c>
+      <c r="F55" t="s">
+        <v>255</v>
+      </c>
+      <c r="G55" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>257</v>
+      </c>
+      <c r="B56" t="s">
+        <v>239</v>
+      </c>
+      <c r="C56" t="s">
+        <v>9</v>
+      </c>
+      <c r="D56" t="s">
+        <v>79</v>
+      </c>
+      <c r="E56" t="s">
+        <v>258</v>
+      </c>
+      <c r="F56" t="s">
+        <v>241</v>
+      </c>
+      <c r="G56" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>260</v>
+      </c>
+      <c r="B57" t="s">
+        <v>261</v>
+      </c>
+      <c r="C57" t="s">
+        <v>9</v>
+      </c>
+      <c r="D57" t="s">
+        <v>84</v>
+      </c>
+      <c r="E57" t="s">
+        <v>262</v>
+      </c>
+      <c r="F57" t="s">
+        <v>263</v>
+      </c>
+      <c r="G57" t="s">
+        <v>264</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>